--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2021_nuble.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2021_nuble.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:42</t>
+    <t xml:space="preserve">2026-10-05 02:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>616910.81</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>630564.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>642121.12</v>
+        <v>642121.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>805474.38</v>
@@ -800,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>652264.12</v>
+        <v>652264.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>815571.81</v>
@@ -836,7 +836,7 @@
         <v>628531.06</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         <v>682964.56</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>713345.12</v>
+        <v>713345.13</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>928044.19</v>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>670928.62</v>
+        <v>670928.63</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>865308.75</v>
@@ -1001,7 +1001,7 @@
         <v>712005.69</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1009,10 +1009,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>709371.12</v>
+        <v>709371.13</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1020,7 +1020,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>717587.12</v>
+        <v>717587.13</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>876325.06</v>
@@ -1053,7 +1053,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>762253.62</v>
+        <v>762253.63</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>930460.56</v>
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>753291.62</v>
+        <v>753291.63</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>927625.75</v>
@@ -1166,7 +1166,7 @@
         <v>785091.31</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1196,7 +1196,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>772982.62</v>
+        <v>772982.63</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>954774.88</v>
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>831529.62</v>
+        <v>831529.63</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1049309.75</v>
@@ -1240,7 +1240,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>784264.62</v>
+        <v>784264.63</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>984727.69</v>
@@ -1287,7 +1287,7 @@
         <v>858036.06</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>861755.44</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1317,7 +1317,7 @@
         <v>59</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>919549.62</v>
+        <v>919549.63</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>1128340.75</v>
@@ -1342,7 +1342,7 @@
         <v>868466.75</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>913289.75</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1419,7 +1419,7 @@
         <v>979991.81</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1482,7 +1482,7 @@
         <v>74</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1017544.12</v>
+        <v>1017544.13</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>1284570.75</v>
@@ -1518,7 +1518,7 @@
         <v>1004061.25</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1537,7 +1537,7 @@
         <v>79</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1015195.12</v>
+        <v>1015195.13</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>1242222.38</v>
@@ -1551,7 +1551,7 @@
         <v>1030642.31</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1050297.38</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1091382.75</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>1075307.62</v>
+        <v>1075307.63</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>1353554.88</v>
